--- a/cancellation_forms/041_child_support_cancellation_form--cancellation_forms.xlsx
+++ b/cancellation_forms/041_child_support_cancellation_form--cancellation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -885,8 +885,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -914,12 +914,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'child_has_reached_the_age_of_majority',_'value':_'age'}</t>
+          <t>child_has_reached_the_age_of_majority</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Child has reached the age of majority', 'value': 'age'}</t>
+          <t>Child has reached the age of majority</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'child_has_joined_the_military',_'value':_'military'}</t>
+          <t>child_has_joined_the_military</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Child has joined the military', 'value': 'military'}</t>
+          <t>Child has joined the military</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'change_in_legal_custody_status',_'value':_'custody'}</t>
+          <t>change_in_legal_custody_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Change in legal custody status', 'value': 'custody'}</t>
+          <t>Change in legal custody status</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'mutual_agreement_between_parents',_'value':_'agreement'}</t>
+          <t>mutual_agreement_between_parents</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Mutual agreement between parents', 'value': 'agreement'}</t>
+          <t>Mutual agreement between parents</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_mutual_consent',_'value':_true}</t>
+          <t>yes_-_mutual_consent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Mutual Consent', 'value': True}</t>
+          <t>Yes - Mutual Consent</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_contested_request',_'value':_false}</t>
+          <t>no_-_contested_request</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'No - Contested Request', 'value': False}</t>
+          <t>No - Contested Request</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_understand',_'value':_true}</t>
+          <t>i_understand</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I Understand', 'value': True}</t>
+          <t>I Understand</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i_disagree',_'value':_false}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I Disagree', 'value': False}</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
